--- a/work_63.xlsx
+++ b/work_63.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A42CBC1-F1DC-45B4-ACCE-6167CDAC86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C456DD5-2679-4DEC-8020-DFB61BB62B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="680" activeTab="5" xr2:uid="{61276BD1-B367-459D-84A4-44FA16EF45B5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="680" activeTab="6" xr2:uid="{61276BD1-B367-459D-84A4-44FA16EF45B5}"/>
   </bookViews>
   <sheets>
     <sheet name="6.3acc自动化验证" sheetId="20" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="292">
   <si>
     <t>cmdb_ci_server.list</t>
     <phoneticPr fontId="1"/>
@@ -5857,13 +5857,103 @@
   </si>
   <si>
     <t>詳細なプロセス, SWインストール一覧, TCP通信状態</t>
+  </si>
+  <si>
+    <t>Credential-less (Nmap)(无凭证降级扫描)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基础硬件分类（依靠端口指纹“猜”出是 Windows 还是 Linux），无法获取深层软件清单。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. 触发条件：
+当上述 IP Range 的凭证登录失败时，作为保底方案自动触发。
+2. MID Server 准备：
+需在 MID Server 上安装并授权 Nmap 引擎。
+3. 网络要求：防火墙必须允许 MID Server 对目标发起大范围端口扫描。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>无需任何账号密码！</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 発動条件: IPレンジの「認証失敗時」のフォールバック(代替手段)として自動作動。
+2. MID要件: Nmapのインストールと実行許可。
+3. ネットワーク: 幅広いポートスキャンの許可。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OSのID/PWは一切不要！</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Credential-less
+(資格情報なし/Nmap)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎的なデバイス分類 (ポート情報からWin/Linux/NW機器を推測)。詳細なプロセス等は取得不可</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6082,6 +6172,32 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -6171,7 +6287,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6208,33 +6324,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6242,9 +6331,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6256,10 +6342,23 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6277,17 +6376,37 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6296,7 +6415,10 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9691,8 +9813,8 @@
       </c>
     </row>
     <row r="42" spans="3:7">
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="8" t="s">
         <v>71</v>
       </c>
@@ -9704,15 +9826,15 @@
       </c>
     </row>
     <row r="43" spans="3:7">
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
     </row>
     <row r="44" spans="3:7">
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="9" t="s">
         <v>72</v>
       </c>
@@ -9724,15 +9846,15 @@
       </c>
     </row>
     <row r="45" spans="3:7">
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
     </row>
     <row r="46" spans="3:7">
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="10"/>
       <c r="F46" s="8" t="s">
         <v>75</v>
@@ -9742,15 +9864,15 @@
       </c>
     </row>
     <row r="47" spans="3:7">
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
     </row>
     <row r="48" spans="3:7">
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="10"/>
       <c r="F48" s="8" t="s">
         <v>76</v>
@@ -9758,8 +9880,8 @@
       <c r="G48" s="10"/>
     </row>
     <row r="49" spans="3:7">
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="8" t="s">
         <v>80</v>
       </c>
@@ -9771,15 +9893,15 @@
       </c>
     </row>
     <row r="50" spans="3:7">
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="9" t="s">
         <v>81</v>
       </c>
@@ -9791,15 +9913,15 @@
       </c>
     </row>
     <row r="52" spans="3:7">
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
     </row>
     <row r="53" spans="3:7">
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="10"/>
       <c r="F53" s="8" t="s">
         <v>84</v>
@@ -9809,7 +9931,7 @@
       </c>
     </row>
     <row r="54" spans="3:7" ht="27.4">
-      <c r="C54" s="12"/>
+      <c r="C54" s="30"/>
       <c r="D54" s="8" t="s">
         <v>88</v>
       </c>
@@ -9824,14 +9946,14 @@
       </c>
     </row>
     <row r="55" spans="3:7">
-      <c r="C55" s="12"/>
+      <c r="C55" s="30"/>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="C56" s="12"/>
+      <c r="C56" s="30"/>
       <c r="D56" s="11" t="s">
         <v>89</v>
       </c>
@@ -9846,14 +9968,14 @@
       </c>
     </row>
     <row r="57" spans="3:7">
-      <c r="C57" s="12"/>
+      <c r="C57" s="30"/>
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="C58" s="12"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="11" t="s">
         <v>90</v>
       </c>
@@ -9862,113 +9984,113 @@
       <c r="G58" s="10"/>
     </row>
     <row r="59" spans="3:7">
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
       <c r="E59" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="60" spans="3:7">
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
       <c r="E60" s="10"/>
       <c r="F60" s="10"/>
-      <c r="G60" s="12"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="3:7">
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
       <c r="E61" s="9" t="s">
         <v>98</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="G61" s="12"/>
+      <c r="G61" s="30"/>
     </row>
     <row r="62" spans="3:7">
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
       <c r="E62" s="10"/>
       <c r="F62" s="10"/>
-      <c r="G62" s="12"/>
+      <c r="G62" s="30"/>
     </row>
     <row r="63" spans="3:7">
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
       <c r="E63" s="10"/>
       <c r="F63" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G63" s="12"/>
+      <c r="G63" s="30"/>
     </row>
     <row r="64" spans="3:7">
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
       <c r="E64" s="8" t="s">
         <v>103</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G64" s="12" t="s">
+      <c r="G64" s="30" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="65" spans="3:7">
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
-      <c r="G65" s="12"/>
+      <c r="G65" s="30"/>
     </row>
     <row r="66" spans="3:7">
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
       <c r="E66" s="9" t="s">
         <v>104</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G66" s="12"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67" spans="3:7">
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
       <c r="E67" s="8" t="s">
         <v>108</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="30" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="68" spans="3:7">
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
-      <c r="G68" s="12"/>
+      <c r="G68" s="30"/>
     </row>
     <row r="69" spans="3:7">
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
       <c r="E69" s="9" t="s">
         <v>109</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="G69" s="12"/>
+      <c r="G69" s="30"/>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" s="8" t="s">
@@ -9994,7 +10116,7 @@
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
     </row>
-    <row r="72" spans="3:7" ht="27">
+    <row r="72" spans="3:7">
       <c r="C72" s="8" t="s">
         <v>114</v>
       </c>
@@ -10037,7 +10159,7 @@
       <c r="G75" s="10"/>
     </row>
     <row r="76" spans="3:7">
-      <c r="C76" s="12"/>
+      <c r="C76" s="30"/>
       <c r="D76" s="8" t="s">
         <v>125</v>
       </c>
@@ -10047,19 +10169,19 @@
       <c r="F76" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="G76" s="30" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="77" spans="3:7">
-      <c r="C77" s="12"/>
+      <c r="C77" s="30"/>
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
+      <c r="G77" s="30"/>
     </row>
     <row r="78" spans="3:7">
-      <c r="C78" s="12"/>
+      <c r="C78" s="30"/>
       <c r="D78" s="11" t="s">
         <v>126</v>
       </c>
@@ -10069,7 +10191,7 @@
       <c r="F78" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="G78" s="12"/>
+      <c r="G78" s="30"/>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" s="8" t="s">
@@ -10084,7 +10206,7 @@
       <c r="F79" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G79" s="30" t="s">
         <v>142</v>
       </c>
     </row>
@@ -10093,7 +10215,7 @@
       <c r="D80" s="10"/>
       <c r="E80" s="10"/>
       <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
+      <c r="G80" s="30"/>
     </row>
     <row r="81" spans="3:7">
       <c r="C81" s="8" t="s">
@@ -10108,14 +10230,14 @@
       <c r="F81" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G81" s="12"/>
+      <c r="G81" s="30"/>
     </row>
     <row r="82" spans="3:7">
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
-      <c r="G82" s="12"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="3:7">
       <c r="C83" s="10"/>
@@ -10124,7 +10246,7 @@
       <c r="F83" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G83" s="12"/>
+      <c r="G83" s="30"/>
     </row>
     <row r="84" spans="3:7">
       <c r="C84" s="11" t="s">
@@ -10133,47 +10255,46 @@
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
-      <c r="G84" s="12"/>
+      <c r="G84" s="30"/>
     </row>
     <row r="85" spans="3:7">
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
       <c r="E85" s="8" t="s">
         <v>143</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G85" s="30" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="86" spans="3:7">
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
-      <c r="G86" s="12"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="3:7">
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
       <c r="E87" s="9" t="s">
         <v>144</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="G87" s="12"/>
+      <c r="G87" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G79:G84"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="G85:G87"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="D42:D48"/>
+    <mergeCell ref="C49:C53"/>
+    <mergeCell ref="D49:D53"/>
+    <mergeCell ref="C54:C58"/>
     <mergeCell ref="G59:G63"/>
     <mergeCell ref="C64:C66"/>
     <mergeCell ref="D64:D66"/>
@@ -10181,13 +10302,14 @@
     <mergeCell ref="C67:C69"/>
     <mergeCell ref="D67:D69"/>
     <mergeCell ref="G67:G69"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="D42:D48"/>
-    <mergeCell ref="C49:C53"/>
-    <mergeCell ref="D49:D53"/>
-    <mergeCell ref="C54:C58"/>
     <mergeCell ref="C59:C63"/>
     <mergeCell ref="D59:D63"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G84"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="G85:G87"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10225,69 +10347,69 @@
       </c>
     </row>
     <row r="35" spans="3:7" ht="45.4" customHeight="1">
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="34" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="3:7">
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="17"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="35"/>
     </row>
     <row r="37" spans="3:7">
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="13" t="s">
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="34" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" spans="3:7">
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="17"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="35"/>
     </row>
     <row r="39" spans="3:7">
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="13" t="s">
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="34" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="40" spans="3:7">
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="17"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="35"/>
     </row>
     <row r="41" spans="3:7">
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="16"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="33"/>
       <c r="F41" s="8" t="s">
         <v>66</v>
       </c>
@@ -10296,12 +10418,12 @@
       </c>
     </row>
     <row r="42" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="13" t="s">
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="31" t="s">
         <v>73</v>
       </c>
       <c r="G42" s="9" t="s">
@@ -10309,17 +10431,17 @@
       </c>
     </row>
     <row r="43" spans="3:7">
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="33"/>
       <c r="G43" s="10"/>
     </row>
     <row r="44" spans="3:7">
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="13" t="s">
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="31" t="s">
         <v>74</v>
       </c>
       <c r="G44" s="9" t="s">
@@ -10327,17 +10449,17 @@
       </c>
     </row>
     <row r="45" spans="3:7">
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="16"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="33"/>
       <c r="G45" s="10"/>
     </row>
     <row r="46" spans="3:7">
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="13" t="s">
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="31" t="s">
         <v>75</v>
       </c>
       <c r="G46" s="9" t="s">
@@ -10345,28 +10467,28 @@
       </c>
     </row>
     <row r="47" spans="3:7">
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="16"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="33"/>
       <c r="G47" s="10"/>
     </row>
     <row r="48" spans="3:7">
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="16"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="33"/>
       <c r="F48" s="8" t="s">
         <v>76</v>
       </c>
       <c r="G48" s="10"/>
     </row>
     <row r="49" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="13" t="s">
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="31" t="s">
         <v>82</v>
       </c>
       <c r="G49" s="9" t="s">
@@ -10374,17 +10496,17 @@
       </c>
     </row>
     <row r="50" spans="3:7">
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="33"/>
       <c r="G50" s="10"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="13" t="s">
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="31" t="s">
         <v>83</v>
       </c>
       <c r="G51" s="9" t="s">
@@ -10392,16 +10514,16 @@
       </c>
     </row>
     <row r="52" spans="3:7">
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="33"/>
       <c r="G52" s="10"/>
     </row>
     <row r="53" spans="3:7">
-      <c r="C53" s="15"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
       <c r="F53" s="8" t="s">
         <v>84</v>
       </c>
@@ -10410,14 +10532,14 @@
       </c>
     </row>
     <row r="54" spans="3:7" ht="43.5" customHeight="1">
-      <c r="C54" s="15"/>
-      <c r="D54" s="13" t="s">
+      <c r="C54" s="32"/>
+      <c r="D54" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="31" t="s">
         <v>93</v>
       </c>
       <c r="G54" s="9" t="s">
@@ -10425,17 +10547,17 @@
       </c>
     </row>
     <row r="55" spans="3:7">
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="16"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="33"/>
       <c r="G55" s="10"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="13" t="s">
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="31" t="s">
         <v>94</v>
       </c>
       <c r="G56" s="9" t="s">
@@ -10443,126 +10565,126 @@
       </c>
     </row>
     <row r="57" spans="3:7">
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
       <c r="G57" s="10"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
       <c r="G58" s="10"/>
     </row>
     <row r="59" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="13" t="s">
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="60" spans="3:7">
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="12"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="3:7">
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="13" t="s">
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="G61" s="12"/>
+      <c r="G61" s="30"/>
     </row>
     <row r="62" spans="3:7">
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="12"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="30"/>
     </row>
     <row r="63" spans="3:7">
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="16"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="33"/>
       <c r="F63" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G63" s="12"/>
+      <c r="G63" s="30"/>
     </row>
     <row r="64" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="13" t="s">
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="G64" s="12" t="s">
+      <c r="G64" s="30" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="65" spans="3:7">
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="12"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="30"/>
     </row>
     <row r="66" spans="3:7">
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="12"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="13" t="s">
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="F67" s="13" t="s">
+      <c r="F67" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="30" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="68" spans="3:7">
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="12"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="30"/>
     </row>
     <row r="69" spans="3:7">
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="12"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="30"/>
     </row>
     <row r="70" spans="3:7" ht="45.4" customHeight="1">
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="E70" s="31" t="s">
         <v>163</v>
       </c>
       <c r="F70" s="8" t="s">
@@ -10573,16 +10695,16 @@
       </c>
     </row>
     <row r="71" spans="3:7">
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
       <c r="F71" s="8"/>
       <c r="G71" s="10"/>
     </row>
     <row r="72" spans="3:7" ht="30.75">
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
       <c r="F72" s="8" t="s">
         <v>169</v>
       </c>
@@ -10591,159 +10713,154 @@
       </c>
     </row>
     <row r="73" spans="3:7">
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
       <c r="F73" s="8"/>
       <c r="G73" s="10"/>
     </row>
     <row r="74" spans="3:7">
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
       <c r="F74" s="8"/>
       <c r="G74" s="10"/>
     </row>
     <row r="75" spans="3:7">
-      <c r="C75" s="15"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
       <c r="F75" s="10"/>
       <c r="G75" s="10"/>
     </row>
     <row r="76" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C76" s="15"/>
-      <c r="D76" s="13" t="s">
+      <c r="C76" s="32"/>
+      <c r="D76" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="31" t="s">
         <v>164</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="G76" s="30" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="77" spans="3:7">
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
       <c r="F77" s="10"/>
-      <c r="G77" s="12"/>
+      <c r="G77" s="30"/>
     </row>
     <row r="78" spans="3:7">
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
       <c r="F78" s="9"/>
-      <c r="G78" s="12"/>
+      <c r="G78" s="30"/>
     </row>
     <row r="79" spans="3:7" ht="45.4" customHeight="1">
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="E79" s="31" t="s">
         <v>165</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G79" s="30" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="80" spans="3:7">
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
       <c r="F80" s="10"/>
-      <c r="G80" s="12"/>
+      <c r="G80" s="30"/>
     </row>
     <row r="81" spans="3:7">
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
+      <c r="C81" s="32"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="32"/>
       <c r="F81" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G81" s="12"/>
+      <c r="G81" s="30"/>
     </row>
     <row r="82" spans="3:7">
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
       <c r="F82" s="10"/>
-      <c r="G82" s="12"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="3:7">
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
       <c r="F83" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G83" s="12"/>
+      <c r="G83" s="30"/>
     </row>
     <row r="84" spans="3:7">
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="16"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="33"/>
       <c r="F84" s="10"/>
-      <c r="G84" s="12"/>
+      <c r="G84" s="30"/>
     </row>
     <row r="85" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="13" t="s">
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="31" t="s">
         <v>166</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G85" s="30" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="86" spans="3:7">
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="15"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
       <c r="F86" s="10"/>
-      <c r="G86" s="12"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="3:7">
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="33"/>
       <c r="F87" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="G87" s="12"/>
+      <c r="G87" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="F67:F69"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="F64:F66"/>
-    <mergeCell ref="F56:F58"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G84"/>
+    <mergeCell ref="G85:G87"/>
+    <mergeCell ref="G59:G63"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="E35:E41"/>
+    <mergeCell ref="E42:E48"/>
+    <mergeCell ref="E49:E53"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="E59:E63"/>
     <mergeCell ref="E67:E69"/>
     <mergeCell ref="C70:C78"/>
     <mergeCell ref="D70:D75"/>
@@ -10754,21 +10871,26 @@
     <mergeCell ref="E76:E78"/>
     <mergeCell ref="E79:E84"/>
     <mergeCell ref="E85:E87"/>
-    <mergeCell ref="E35:E41"/>
-    <mergeCell ref="E42:E48"/>
-    <mergeCell ref="E49:E53"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="E64:E66"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G79:G84"/>
-    <mergeCell ref="G85:G87"/>
-    <mergeCell ref="G59:G63"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="G67:G69"/>
     <mergeCell ref="C35:C69"/>
     <mergeCell ref="D35:D53"/>
     <mergeCell ref="D54:D69"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="F67:F69"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="F56:F58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10806,69 +10928,69 @@
       </c>
     </row>
     <row r="35" spans="3:7" ht="45.4" customHeight="1">
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="30" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="3:7">
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="12"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="3:7">
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18" t="s">
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="30" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" spans="3:7">
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="12"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="30"/>
     </row>
     <row r="39" spans="3:7">
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18" t="s">
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="30" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="40" spans="3:7">
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="12"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="30"/>
     </row>
     <row r="41" spans="3:7">
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
       <c r="F41" s="8" t="s">
         <v>66</v>
       </c>
@@ -10877,12 +10999,12 @@
       </c>
     </row>
     <row r="42" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18" t="s">
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="36" t="s">
         <v>73</v>
       </c>
       <c r="G42" s="9" t="s">
@@ -10890,17 +11012,17 @@
       </c>
     </row>
     <row r="43" spans="3:7">
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
       <c r="G43" s="10"/>
     </row>
     <row r="44" spans="3:7">
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18" t="s">
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36" t="s">
         <v>74</v>
       </c>
       <c r="G44" s="9" t="s">
@@ -10908,17 +11030,17 @@
       </c>
     </row>
     <row r="45" spans="3:7">
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
       <c r="G45" s="10"/>
     </row>
     <row r="46" spans="3:7">
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18" t="s">
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36" t="s">
         <v>75</v>
       </c>
       <c r="G46" s="9" t="s">
@@ -10926,28 +11048,28 @@
       </c>
     </row>
     <row r="47" spans="3:7">
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
       <c r="G47" s="10"/>
     </row>
     <row r="48" spans="3:7">
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
       <c r="F48" s="8" t="s">
         <v>76</v>
       </c>
       <c r="G48" s="10"/>
     </row>
     <row r="49" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18" t="s">
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="F49" s="18" t="s">
+      <c r="F49" s="36" t="s">
         <v>172</v>
       </c>
       <c r="G49" s="9" t="s">
@@ -10955,17 +11077,17 @@
       </c>
     </row>
     <row r="50" spans="3:7">
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
       <c r="G50" s="10"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18" t="s">
+      <c r="C51" s="36"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36" t="s">
         <v>83</v>
       </c>
       <c r="G51" s="9" t="s">
@@ -10973,16 +11095,16 @@
       </c>
     </row>
     <row r="52" spans="3:7">
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
       <c r="G52" s="10"/>
     </row>
     <row r="53" spans="3:7">
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="8" t="s">
         <v>84</v>
       </c>
@@ -10991,14 +11113,14 @@
       </c>
     </row>
     <row r="54" spans="3:7" ht="43.5" customHeight="1">
-      <c r="C54" s="18"/>
-      <c r="D54" s="18" t="s">
+      <c r="C54" s="36"/>
+      <c r="D54" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="E54" s="18" t="s">
+      <c r="E54" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="F54" s="37" t="s">
         <v>170</v>
       </c>
       <c r="G54" s="9" t="s">
@@ -11006,115 +11128,115 @@
       </c>
     </row>
     <row r="55" spans="3:7">
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
       <c r="G55" s="10"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
       <c r="G56" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="57" spans="3:7">
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
       <c r="G57" s="10"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
       <c r="G58" s="10"/>
     </row>
     <row r="59" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18" t="s">
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F59" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="60" spans="3:7">
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="12"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="3:7">
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18" t="s">
+      <c r="C61" s="36"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="G61" s="12"/>
+      <c r="G61" s="30"/>
     </row>
     <row r="62" spans="3:7">
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="12"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="30"/>
     </row>
     <row r="63" spans="3:7">
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
       <c r="F63" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G63" s="12"/>
+      <c r="G63" s="30"/>
     </row>
     <row r="64" spans="3:7" ht="29.65" customHeight="1">
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18" t="s">
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="18" t="s">
+      <c r="F64" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="G64" s="12" t="s">
+      <c r="G64" s="30" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="65" spans="3:7">
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="12"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="30"/>
     </row>
     <row r="66" spans="3:7">
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="12"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67" spans="3:7" ht="45.4" customHeight="1">
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="E67" s="18" t="s">
+      <c r="E67" s="36" t="s">
         <v>163</v>
       </c>
       <c r="F67" s="8" t="s">
@@ -11125,16 +11247,16 @@
       </c>
     </row>
     <row r="68" spans="3:7">
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
       <c r="F68" s="8"/>
       <c r="G68" s="10"/>
     </row>
     <row r="69" spans="3:7" ht="30.75">
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
       <c r="F69" s="8" t="s">
         <v>169</v>
       </c>
@@ -11143,28 +11265,42 @@
       </c>
     </row>
     <row r="70" spans="3:7">
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
       <c r="F70" s="8"/>
       <c r="G70" s="10"/>
     </row>
     <row r="71" spans="3:7">
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
       <c r="F71" s="8"/>
       <c r="G71" s="10"/>
     </row>
     <row r="72" spans="3:7">
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
       <c r="F72" s="10"/>
       <c r="G72" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="E35:E41"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="E49:E53"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="E42:E48"/>
     <mergeCell ref="C67:C72"/>
     <mergeCell ref="D67:D72"/>
     <mergeCell ref="E67:E72"/>
@@ -11179,22 +11315,8 @@
     <mergeCell ref="F56:F58"/>
     <mergeCell ref="E59:E63"/>
     <mergeCell ref="F59:F60"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="E49:E53"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="F51:F52"/>
     <mergeCell ref="C35:C66"/>
     <mergeCell ref="D35:D53"/>
-    <mergeCell ref="E35:E41"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="E42:E48"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11210,298 +11332,312 @@
     <col min="1" max="5" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="41.65">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="38" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-    </row>
-    <row r="3" spans="1:5" ht="54">
-      <c r="A3" s="24" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-    </row>
-    <row r="4" spans="1:5" ht="27.75">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="20" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="38" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-    </row>
-    <row r="6" spans="1:5" ht="41.65">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="25" t="s">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:5" ht="40.5">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="20" t="s">
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="13" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.75">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="20" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="13" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.75">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" s="38"/>
+      <c r="B9" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="38" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-    </row>
-    <row r="11" spans="1:5" ht="55.5">
-      <c r="A11" s="22"/>
-      <c r="B11" s="25" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="38"/>
+      <c r="B11" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-    </row>
-    <row r="13" spans="1:5" ht="27.75">
-      <c r="A13" s="22"/>
-      <c r="B13" s="25" t="s">
+      <c r="A12" s="38"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="38"/>
+      <c r="B13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-    </row>
-    <row r="14" spans="1:5" ht="41.65">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="20" t="s">
+      <c r="C13" s="39"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="13" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.75">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="20" t="s">
+    <row r="15" spans="1:5" ht="27">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="13" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="40.5">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="20" t="s">
+    <row r="16" spans="1:5" ht="27">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="13" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="41.65">
-      <c r="A17" s="20" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="21"/>
-    </row>
-    <row r="19" spans="1:5" ht="41.65">
-      <c r="A19" s="24" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="21"/>
-    </row>
-    <row r="20" spans="1:5" ht="27.75">
-      <c r="A20" s="22"/>
-      <c r="B20" s="20" t="s">
+      <c r="C19" s="39"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="39"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="38"/>
+      <c r="B20" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="38" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-    </row>
-    <row r="22" spans="1:5" ht="41.65">
-      <c r="A22" s="22"/>
-      <c r="B22" s="25" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="38"/>
+      <c r="B22" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-    </row>
-    <row r="23" spans="1:5" ht="41.65">
-      <c r="A23" s="20" t="s">
+      <c r="C22" s="39"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="38" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-    </row>
-    <row r="25" spans="1:5" ht="55.5">
-      <c r="A25" s="24" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-    </row>
-    <row r="26" spans="1:5" ht="41.65">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="20" t="s">
+      <c r="C25" s="39"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+    </row>
+    <row r="26" spans="1:5" ht="27">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="13" t="s">
         <v>221</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="D20:D22"/>
@@ -11509,20 +11645,6 @@
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="D23:D25"/>
     <mergeCell ref="E23:E25"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="C9:C13"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11534,166 +11656,179 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="11.8125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="23.125" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5625" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.0625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="65.6875" style="27" customWidth="1"/>
-    <col min="5" max="5" width="49.9375" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.8125" style="27"/>
+    <col min="1" max="1" width="23.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.0625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65.6875" style="17" customWidth="1"/>
+    <col min="5" max="5" width="49.9375" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.8125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="61.5" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="18" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="18" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="29" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D5" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E5" s="18" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="29" t="s">
+    <row r="6" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D6" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A6" s="30"/>
-      <c r="B6" s="32" t="s">
+    <row r="7" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A7" s="25"/>
+      <c r="B7" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C7" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D7" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A7" s="30"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="29" t="s">
+    <row r="8" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A8" s="25"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D8" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A8" s="30"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="29" t="s">
+    <row r="9" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A9" s="25"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D9" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="29" t="s">
+    <row r="10" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A10" s="26"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D10" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E10" s="18" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="99.4" customHeight="1">
-      <c r="A10" s="29" t="s">
+    <row r="11" spans="1:5" ht="99.4" customHeight="1">
+      <c r="A11" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B11" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C11" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D11" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E11" s="18" t="s">
         <v>254</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11705,196 +11840,212 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="11.8125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.4375" style="37" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.8125" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.25" style="37" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.125" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.8125" style="37"/>
+    <col min="1" max="1" width="31.4375" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.8125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.25" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.8125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="39" t="s">
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="94.15" customHeight="1">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-    </row>
-    <row r="4" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+    </row>
+    <row r="4" spans="1:8" ht="66">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+    </row>
+    <row r="5" spans="1:8" ht="84.4" customHeight="1">
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D5" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E5" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-    </row>
-    <row r="5" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A5" s="40"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="39" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="84.4" customHeight="1">
+      <c r="A6" s="41"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D6" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E6" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-    </row>
-    <row r="6" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A6" s="40"/>
-      <c r="B6" s="38" t="s">
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="84.4" customHeight="1">
+      <c r="A7" s="41"/>
+      <c r="B7" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C7" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D7" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E7" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-    </row>
-    <row r="7" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="39" t="s">
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="84.4" customHeight="1">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D8" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E8" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-    </row>
-    <row r="8" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" ht="84.4" customHeight="1">
       <c r="A9" s="41"/>
       <c r="B9" s="41"/>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" ht="84.4" customHeight="1">
+      <c r="A10" s="42"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D10" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E10" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-    </row>
-    <row r="10" spans="1:8" ht="84.4" customHeight="1">
-      <c r="A10" s="42" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" ht="84.4" customHeight="1">
+      <c r="A11" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B11" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C11" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D11" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E11" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
